--- a/public/ModeleImportationVente.xlsx
+++ b/public/ModeleImportationVente.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Angelo\Strong Africa\magcarburant\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0718C7-8EE8-4A79-837C-794BE5643B2D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996DF19B-85B7-4D95-8C80-CC3447513206}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
   <si>
     <t>LOCALITE</t>
   </si>
@@ -36,9 +36,6 @@
     <t>PRODUIT</t>
   </si>
   <si>
-    <t>DATE</t>
-  </si>
-  <si>
     <t>BON DE LIVRAISON</t>
   </si>
   <si>
@@ -103,6 +100,12 @@
   </si>
   <si>
     <t>ESSENCE | GASOIL | PETROLE | FOMI</t>
+  </si>
+  <si>
+    <t>TERMINAL</t>
+  </si>
+  <si>
+    <t>DATE VENTE</t>
   </si>
 </sst>
 </file>
@@ -222,10 +225,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{19F7D991-8B48-4FF8-AFEB-6BB05DB3E7F3}" name="Table2" displayName="Table2" ref="A1:J3000" totalsRowShown="0">
-  <autoFilter ref="A1:J3000" xr:uid="{AF117FD5-8164-4E05-8B07-2900E9EE5898}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{8D554587-CD84-4BCF-B85E-4BE46737C068}" name="DATE"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{19F7D991-8B48-4FF8-AFEB-6BB05DB3E7F3}" name="Table2" displayName="Table2" ref="A1:K3000" totalsRowShown="0">
+  <autoFilter ref="A1:K3000" xr:uid="{AF117FD5-8164-4E05-8B07-2900E9EE5898}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{8D554587-CD84-4BCF-B85E-4BE46737C068}" name="DATE VENTE"/>
+    <tableColumn id="6" xr3:uid="{8754ED5D-CB5B-4850-9AB9-21D41C1894B2}" name="TERMINAL"/>
     <tableColumn id="11" xr3:uid="{98A8B8F4-D469-455A-B116-4FAF4CC916BD}" name="LOCALITE"/>
     <tableColumn id="2" xr3:uid="{535FEAF1-2FAB-472B-883E-84B0E23284B8}" name="VOIE"/>
     <tableColumn id="3" xr3:uid="{B0AAAA7B-B49B-4213-93C6-F9127F532F52}" name="PRODUIT"/>
@@ -241,8 +245,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FA5846F-6F47-404A-B63D-D6A664F5F8F2}" name="Table3" displayName="Table3" ref="M12:O22" totalsRowShown="0">
-  <autoFilter ref="M12:O22" xr:uid="{E604AD25-C887-4B63-994B-5EA9D7B91566}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2FA5846F-6F47-404A-B63D-D6A664F5F8F2}" name="Table3" displayName="Table3" ref="N12:P24" totalsRowShown="0">
+  <autoFilter ref="N12:P24" xr:uid="{E604AD25-C887-4B63-994B-5EA9D7B91566}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{AA7EFDBF-8637-45B5-968C-6EA4D0B830F7}" name="Colonne"/>
     <tableColumn id="2" xr3:uid="{447E7B6C-EDEA-45E5-B1E4-C90D91D49841}" name="Type de données" dataDxfId="1"/>
@@ -515,310 +519,327 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="33.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E2" s="3"/>
-      <c r="M2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" s="6"/>
+    </row>
+    <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F2" s="3"/>
+      <c r="N2" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="O2" s="6"/>
-      <c r="P2" s="4"/>
+      <c r="P2" s="6"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
-    </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E3" s="3"/>
-      <c r="M3" s="6"/>
+      <c r="U2" s="4"/>
+    </row>
+    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F3" s="3"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
-      <c r="P3" s="4"/>
+      <c r="P3" s="6"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E4" s="3"/>
-      <c r="N4" s="5"/>
+      <c r="U3" s="4"/>
+    </row>
+    <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F4" s="3"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
-    </row>
-    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E5" s="3"/>
-      <c r="M5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="N5" s="7"/>
+      <c r="U4" s="5"/>
+    </row>
+    <row r="5" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F5" s="3"/>
+      <c r="N5" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="O5" s="7"/>
-      <c r="P5" s="5"/>
+      <c r="P5" s="7"/>
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
-    </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E6" s="3"/>
-      <c r="M6" s="7"/>
+      <c r="U5" s="5"/>
+    </row>
+    <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F6" s="3"/>
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
-      <c r="P6" s="5"/>
+      <c r="P6" s="7"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
-    </row>
-    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E7" s="3"/>
-      <c r="M7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N7" s="8"/>
+      <c r="U6" s="5"/>
+    </row>
+    <row r="7" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F7" s="3"/>
+      <c r="N7" s="8" t="s">
+        <v>10</v>
+      </c>
       <c r="O7" s="8"/>
-      <c r="P7" s="5"/>
+      <c r="P7" s="8"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5"/>
-    </row>
-    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="3"/>
-      <c r="M8" s="8"/>
+      <c r="U7" s="5"/>
+    </row>
+    <row r="8" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F8" s="3"/>
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
-      <c r="P8" s="5"/>
+      <c r="P8" s="8"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5"/>
-    </row>
-    <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E9" s="3"/>
-      <c r="M9" s="8"/>
+      <c r="U8" s="5"/>
+    </row>
+    <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F9" s="3"/>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
-      <c r="P9" s="5"/>
+      <c r="P9" s="8"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5"/>
-    </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E10" s="3"/>
-      <c r="M10" s="8"/>
+      <c r="U9" s="5"/>
+    </row>
+    <row r="10" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F10" s="3"/>
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
-      <c r="P10" s="5"/>
+      <c r="P10" s="8"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E12" s="3"/>
-      <c r="M12" t="s">
+      <c r="U10" s="5"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="F12" s="3"/>
+      <c r="N12" t="s">
+        <v>11</v>
+      </c>
+      <c r="O12" t="s">
         <v>12</v>
       </c>
-      <c r="N12" t="s">
+      <c r="P12" t="s">
         <v>13</v>
       </c>
-      <c r="O12" t="s">
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="F13" s="3"/>
+      <c r="N13" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="F14" s="3"/>
+      <c r="N14" t="s">
+        <v>25</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="F15" s="3"/>
+      <c r="N15" t="s">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="F16" s="3"/>
+      <c r="N16" t="s">
+        <v>1</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P16" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E13" s="3"/>
-      <c r="M13" t="s">
+    <row r="17" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F17" s="3"/>
+      <c r="N17" t="s">
+        <v>2</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F18" s="3"/>
+      <c r="N18" t="s">
         <v>3</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="O18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F19" s="3"/>
+      <c r="N19" t="s">
+        <v>4</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F20" s="3"/>
+      <c r="N20" t="s">
+        <v>5</v>
+      </c>
+      <c r="O20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E14" s="3"/>
-      <c r="M14" t="s">
-        <v>0</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E15" s="3"/>
-      <c r="M15" t="s">
-        <v>1</v>
-      </c>
-      <c r="N15" s="2" t="s">
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F21" s="3"/>
+      <c r="N21" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="O15" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E16" s="3"/>
-      <c r="M16" t="s">
-        <v>2</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E17" s="3"/>
-      <c r="M17" t="s">
-        <v>4</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E18" s="3"/>
-      <c r="M18" t="s">
-        <v>5</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O18" s="1"/>
-    </row>
-    <row r="19" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E19" s="3"/>
-      <c r="M19" t="s">
-        <v>6</v>
-      </c>
-      <c r="N19" s="2" t="s">
+      <c r="P21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="O19" s="1"/>
-    </row>
-    <row r="20" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E20" s="3"/>
-      <c r="M20" t="s">
-        <v>24</v>
-      </c>
-      <c r="N20" s="2" t="s">
+    </row>
+    <row r="22" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F22" s="3"/>
+      <c r="N22" t="s">
+        <v>7</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="O20" s="1" t="s">
+    </row>
+    <row r="23" spans="6:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F23" s="3"/>
+      <c r="N23" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="6:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F24" s="3"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F25" s="3"/>
+    </row>
+    <row r="28" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="N28" s="9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E21" s="3"/>
-      <c r="M21" t="s">
-        <v>8</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E22" s="3"/>
-      <c r="M22" t="s">
-        <v>9</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="5:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="5:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E24" s="3"/>
-      <c r="M24" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-    </row>
-    <row r="25" spans="5:15" x14ac:dyDescent="0.25">
-      <c r="E25" s="3"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+    </row>
+    <row r="29" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M2:O3"/>
-    <mergeCell ref="M5:O6"/>
-    <mergeCell ref="M7:O10"/>
-    <mergeCell ref="M24:O25"/>
+    <mergeCell ref="N2:P3"/>
+    <mergeCell ref="N5:P6"/>
+    <mergeCell ref="N7:P10"/>
+    <mergeCell ref="N28:P29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
